--- a/Catch and index models/JABBA_macarellus/jabba_priori_posteriori.xlsx
+++ b/Catch and index models/JABBA_macarellus/jabba_priori_posteriori.xlsx
@@ -483,16 +483,16 @@
         <v>0.3971213521963843</v>
       </c>
       <c r="D2">
-        <v>0.383188747555341</v>
+        <v>0.3464505547080821</v>
       </c>
       <c r="E2">
-        <v>0.9649160022144734</v>
+        <v>0.8724047518269819</v>
       </c>
       <c r="F2">
-        <v>-14.34441475734769</v>
+        <v>-18.97673845423784</v>
       </c>
       <c r="G2">
-        <v>0.8911</v>
+        <v>0.8723</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -506,16 +506,16 @@
         <v>24372.87040922948</v>
       </c>
       <c r="D3">
-        <v>36222.04582837179</v>
+        <v>31109.93120960912</v>
       </c>
       <c r="E3">
-        <v>1.486162492155839</v>
+        <v>1.276416387863305</v>
       </c>
       <c r="F3">
-        <v>4.956559423366924</v>
+        <v>6.40182617633267</v>
       </c>
       <c r="G3">
-        <v>0.9709</v>
+        <v>0.9714</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -529,16 +529,16 @@
         <v>2411.135802223795</v>
       </c>
       <c r="D4">
-        <v>3604.71273960018</v>
+        <v>2764.218866491746</v>
       </c>
       <c r="E4">
-        <v>1.495026840162029</v>
+        <v>1.146438480960841</v>
       </c>
       <c r="F4">
-        <v>1.75016288985308</v>
+        <v>7.055882823314663</v>
       </c>
       <c r="G4">
-        <v>0.9727</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -549,19 +549,19 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>0.9020966268301949</v>
+        <v>0.6311221931084887</v>
       </c>
       <c r="D5">
-        <v>0.8613404453998348</v>
+        <v>0.6237815231714869</v>
       </c>
       <c r="E5">
-        <v>0.9548206032278715</v>
+        <v>0.9883688610269804</v>
       </c>
       <c r="F5">
-        <v>17.26489293251536</v>
+        <v>1.774182106145628</v>
       </c>
       <c r="G5">
-        <v>0.9540999999999999</v>
+        <v>0.9439</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -575,16 +575,16 @@
         <v>0.002722461526595033</v>
       </c>
       <c r="D6">
-        <v>0.003285032647981125</v>
+        <v>0.003362487361482206</v>
       </c>
       <c r="E6">
-        <v>1.206640613977637</v>
+        <v>1.235090864879053</v>
       </c>
       <c r="F6">
-        <v>-255.4146692808708</v>
+        <v>-232.1370555944168</v>
       </c>
       <c r="G6">
-        <v>0.8761</v>
+        <v>0.8885999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -598,16 +598,16 @@
         <v>0.4007686155536355</v>
       </c>
       <c r="D7">
-        <v>0.4579160144097594</v>
+        <v>0.4693709415875138</v>
       </c>
       <c r="E7">
-        <v>1.142594496271068</v>
+        <v>1.171176892030602</v>
       </c>
       <c r="F7">
-        <v>-15.1571567809544</v>
+        <v>-22.22290614519398</v>
       </c>
       <c r="G7">
-        <v>0.9307</v>
+        <v>0.9075</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -621,13 +621,13 @@
         <v>24336.8599463856</v>
       </c>
       <c r="D8">
-        <v>21155.77463178938</v>
+        <v>20769.8344215914</v>
       </c>
       <c r="E8">
-        <v>0.869289410318168</v>
+        <v>0.8534311520610136</v>
       </c>
       <c r="F8">
-        <v>59.59631108831196</v>
+        <v>49.39604920173159</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -644,16 +644,16 @@
         <v>2429.940192410308</v>
       </c>
       <c r="D9">
-        <v>2119.049295383454</v>
+        <v>2165.232021973961</v>
       </c>
       <c r="E9">
-        <v>0.8720582103222569</v>
+        <v>0.8910639153740746</v>
       </c>
       <c r="F9">
-        <v>56.25744534583617</v>
+        <v>57.81514864955224</v>
       </c>
       <c r="G9">
-        <v>0.9995000000000001</v>
+        <v>0.9987</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -664,19 +664,19 @@
         <v>11</v>
       </c>
       <c r="C10">
-        <v>0.89590749532111</v>
+        <v>0.6278077650934539</v>
       </c>
       <c r="D10">
-        <v>0.759095258215791</v>
+        <v>0.571450285334551</v>
       </c>
       <c r="E10">
-        <v>0.8472920052351132</v>
+        <v>0.9102313114102473</v>
       </c>
       <c r="F10">
-        <v>20.42244009074865</v>
+        <v>11.33982156923614</v>
       </c>
       <c r="G10">
-        <v>0.9005</v>
+        <v>0.9267</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -690,16 +690,16 @@
         <v>0.002721661204586427</v>
       </c>
       <c r="D11">
-        <v>0.00318884724649142</v>
+        <v>0.003118177619943676</v>
       </c>
       <c r="E11">
-        <v>1.171654738333233</v>
+        <v>1.145689116150481</v>
       </c>
       <c r="F11">
-        <v>-140.04603473114</v>
+        <v>-63.91525126972608</v>
       </c>
       <c r="G11">
-        <v>0.8738</v>
+        <v>0.9201</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -713,16 +713,16 @@
         <v>0.3997252876323918</v>
       </c>
       <c r="D12">
-        <v>0.5155832125484976</v>
+        <v>0.4790747195590728</v>
       </c>
       <c r="E12">
-        <v>1.289843871530727</v>
+        <v>1.198509912636938</v>
       </c>
       <c r="F12">
-        <v>-25.39052176542342</v>
+        <v>-17.85463490865567</v>
       </c>
       <c r="G12">
-        <v>0.8885999999999999</v>
+        <v>0.9117</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -736,16 +736,16 @@
         <v>24088.18035104122</v>
       </c>
       <c r="D13">
-        <v>26826.00941171006</v>
+        <v>27305.16138785595</v>
       </c>
       <c r="E13">
-        <v>1.113658608527916</v>
+        <v>1.13355018892806</v>
       </c>
       <c r="F13">
-        <v>59.49199970670229</v>
+        <v>53.3391617094567</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -759,16 +759,16 @@
         <v>2395.445409853768</v>
       </c>
       <c r="D14">
-        <v>3297.144274208255</v>
+        <v>3135.115784052506</v>
       </c>
       <c r="E14">
-        <v>1.376422213858562</v>
+        <v>1.308781978982311</v>
       </c>
       <c r="F14">
-        <v>59.76123170649421</v>
+        <v>59.37948483980373</v>
       </c>
       <c r="G14">
-        <v>0.9994</v>
+        <v>0.9992</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -779,19 +779,19 @@
         <v>11</v>
       </c>
       <c r="C15">
-        <v>0.9009089089687622</v>
+        <v>0.6304865574855016</v>
       </c>
       <c r="D15">
-        <v>0.7916828919361751</v>
+        <v>0.5877246473592117</v>
       </c>
       <c r="E15">
-        <v>0.878760198789005</v>
+        <v>0.9321763333117958</v>
       </c>
       <c r="F15">
-        <v>16.83563544334316</v>
+        <v>8.976320171790686</v>
       </c>
       <c r="G15">
-        <v>0.917</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -805,16 +805,16 @@
         <v>0.002710217495919815</v>
       </c>
       <c r="D16">
-        <v>0.003046415341605357</v>
+        <v>0.003339792332215349</v>
       </c>
       <c r="E16">
-        <v>1.124048289922002</v>
+        <v>1.232296794350766</v>
       </c>
       <c r="F16">
-        <v>-13.11075072156189</v>
+        <v>-54.97396150046639</v>
       </c>
       <c r="G16">
-        <v>0.9569</v>
+        <v>0.9239000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -828,16 +828,16 @@
         <v>0.3961756540002593</v>
       </c>
       <c r="D17">
-        <v>0.4758049804755395</v>
+        <v>0.3950392108694818</v>
       </c>
       <c r="E17">
-        <v>1.200995002270453</v>
+        <v>0.9971314665116277</v>
       </c>
       <c r="F17">
-        <v>-13.15751579397757</v>
+        <v>-13.60736046311724</v>
       </c>
       <c r="G17">
-        <v>0.924</v>
+        <v>0.9268999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -851,16 +851,16 @@
         <v>24079.87094980434</v>
       </c>
       <c r="D18">
-        <v>31392.36456368883</v>
+        <v>24974.50723244638</v>
       </c>
       <c r="E18">
-        <v>1.303676611437318</v>
+        <v>1.037152868655607</v>
       </c>
       <c r="F18">
-        <v>27.04095559404163</v>
+        <v>39.80278237231985</v>
       </c>
       <c r="G18">
-        <v>0.9923</v>
+        <v>0.9913</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -874,16 +874,16 @@
         <v>2396.511668368277</v>
       </c>
       <c r="D19">
-        <v>3582.736364755819</v>
+        <v>2141.147939962468</v>
       </c>
       <c r="E19">
-        <v>1.494979729097339</v>
+        <v>0.8934435697616778</v>
       </c>
       <c r="F19">
-        <v>33.00124104138617</v>
+        <v>37.38169360562173</v>
       </c>
       <c r="G19">
-        <v>0.9906</v>
+        <v>0.9903</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -894,19 +894,19 @@
         <v>11</v>
       </c>
       <c r="C20">
-        <v>0.9013981432482688</v>
+        <v>0.6307484067056155</v>
       </c>
       <c r="D20">
-        <v>0.8837855329450415</v>
+        <v>0.6383218847900659</v>
       </c>
       <c r="E20">
-        <v>0.9804607870172012</v>
+        <v>1.012007129949018</v>
       </c>
       <c r="F20">
-        <v>18.87232418987981</v>
+        <v>0.5347562852303867</v>
       </c>
       <c r="G20">
-        <v>0.9719</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -920,16 +920,16 @@
         <v>0.002720766011461618</v>
       </c>
       <c r="D21">
-        <v>0.002832269060181836</v>
+        <v>0.002759096151663624</v>
       </c>
       <c r="E21">
-        <v>1.040982226420977</v>
+        <v>1.014087995821962</v>
       </c>
       <c r="F21">
-        <v>-9.857231603984729</v>
+        <v>-7.254068241473388</v>
       </c>
       <c r="G21">
-        <v>0.952</v>
+        <v>0.9446</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -943,16 +943,16 @@
         <v>0.4000478167436514</v>
       </c>
       <c r="D22">
-        <v>0.4998955762278293</v>
+        <v>0.4766639297933654</v>
       </c>
       <c r="E22">
-        <v>1.249589562310147</v>
+        <v>1.191517388279634</v>
       </c>
       <c r="F22">
-        <v>-12.77032335342703</v>
+        <v>-7.975806801731933</v>
       </c>
       <c r="G22">
-        <v>0.9213</v>
+        <v>0.9365</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -966,13 +966,13 @@
         <v>24204.27178920261</v>
       </c>
       <c r="D23">
-        <v>22873.71515309571</v>
+        <v>22797.18456448815</v>
       </c>
       <c r="E23">
-        <v>0.9450280244869645</v>
+        <v>0.9418661616028391</v>
       </c>
       <c r="F23">
-        <v>50.58457930751678</v>
+        <v>56.67564105399003</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -989,16 +989,16 @@
         <v>3545.753981547758</v>
       </c>
       <c r="D24">
-        <v>4027.771232382639</v>
+        <v>3818.564722567396</v>
       </c>
       <c r="E24">
-        <v>1.13594210239721</v>
+        <v>1.076940121181378</v>
       </c>
       <c r="F24">
-        <v>55.74673298727604</v>
+        <v>59.32293914112001</v>
       </c>
       <c r="G24">
-        <v>0.999</v>
+        <v>0.9999</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1009,19 +1009,19 @@
         <v>11</v>
       </c>
       <c r="C25">
-        <v>0.9011295279918223</v>
+        <v>0.6306046419251319</v>
       </c>
       <c r="D25">
-        <v>0.7905625087181893</v>
+        <v>0.5957444859518122</v>
       </c>
       <c r="E25">
-        <v>0.877301746486953</v>
+        <v>0.9447194745238516</v>
       </c>
       <c r="F25">
-        <v>23.4660515651624</v>
+        <v>6.377599071269624</v>
       </c>
       <c r="G25">
-        <v>0.9429</v>
+        <v>0.9474</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1035,16 +1035,16 @@
         <v>0.002740789779712745</v>
       </c>
       <c r="D26">
-        <v>0.003159216409802107</v>
+        <v>0.002573949760145481</v>
       </c>
       <c r="E26">
-        <v>1.152666444244117</v>
+        <v>0.9391270279821496</v>
       </c>
       <c r="F26">
-        <v>-36.36513969246553</v>
+        <v>18.32250819470199</v>
       </c>
       <c r="G26">
-        <v>0.9366</v>
+        <v>0.9611</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1058,16 +1058,16 @@
         <v>0.2234676835744281</v>
       </c>
       <c r="D27">
-        <v>0.3105704894947038</v>
+        <v>0.3011581076203112</v>
       </c>
       <c r="E27">
-        <v>1.389778085703677</v>
+        <v>1.347658430083505</v>
       </c>
       <c r="F27">
-        <v>-31.9964231802202</v>
+        <v>-35.58091221396425</v>
       </c>
       <c r="G27">
-        <v>0.8808</v>
+        <v>0.8966</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1081,16 +1081,16 @@
         <v>23755.54044574203</v>
       </c>
       <c r="D28">
-        <v>39390.53042558488</v>
+        <v>38643.56514160557</v>
       </c>
       <c r="E28">
-        <v>1.658161830312948</v>
+        <v>1.626717995739477</v>
       </c>
       <c r="F28">
-        <v>39.99807152926763</v>
+        <v>32.17634501143271</v>
       </c>
       <c r="G28">
-        <v>0.9966</v>
+        <v>0.9962</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1104,16 +1104,16 @@
         <v>1328.734476676153</v>
       </c>
       <c r="D29">
-        <v>2951.33419215964</v>
+        <v>2853.138864567934</v>
       </c>
       <c r="E29">
-        <v>2.221161747486557</v>
+        <v>2.147260355360913</v>
       </c>
       <c r="F29">
-        <v>35.81643006588916</v>
+        <v>44.27424498269669</v>
       </c>
       <c r="G29">
-        <v>0.9907</v>
+        <v>0.9929</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1124,19 +1124,19 @@
         <v>11</v>
       </c>
       <c r="C30">
-        <v>0.9000192065666849</v>
+        <v>0.6300102828166092</v>
       </c>
       <c r="D30">
-        <v>0.7612614702424085</v>
+        <v>0.5744121768244594</v>
       </c>
       <c r="E30">
-        <v>0.8458280275444373</v>
+        <v>0.9117504785103104</v>
       </c>
       <c r="F30">
-        <v>22.84355389694803</v>
+        <v>13.73536943593794</v>
       </c>
       <c r="G30">
-        <v>0.9066</v>
+        <v>0.9371</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1150,16 +1150,16 @@
         <v>0.002711212114769038</v>
       </c>
       <c r="D31">
-        <v>0.003559549359421831</v>
+        <v>0.003314026746746525</v>
       </c>
       <c r="E31">
-        <v>1.312899621549921</v>
+        <v>1.22234137590848</v>
       </c>
       <c r="F31">
-        <v>-80.5185890317333</v>
+        <v>-26.16650099135462</v>
       </c>
       <c r="G31">
-        <v>0.8851</v>
+        <v>0.9456</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1173,16 +1173,16 @@
         <v>0.6911131929887162</v>
       </c>
       <c r="D32">
-        <v>0.8007338831870298</v>
+        <v>0.7701690876681926</v>
       </c>
       <c r="E32">
-        <v>1.158614668784225</v>
+        <v>1.114389213636046</v>
       </c>
       <c r="F32">
-        <v>-13.61056530555478</v>
+        <v>-7.34421415066786</v>
       </c>
       <c r="G32">
-        <v>0.9199000000000001</v>
+        <v>0.9369</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1196,13 +1196,13 @@
         <v>23988.90399300415</v>
       </c>
       <c r="D33">
-        <v>18141.84394932003</v>
+        <v>17746.11781298092</v>
       </c>
       <c r="E33">
-        <v>0.7562598088937582</v>
+        <v>0.7397635931243958</v>
       </c>
       <c r="F33">
-        <v>65.05599974523854</v>
+        <v>71.1918340924569</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1219,16 +1219,16 @@
         <v>4168.389082824915</v>
       </c>
       <c r="D34">
-        <v>3491.48202773739</v>
+        <v>3249.56937857029</v>
       </c>
       <c r="E34">
-        <v>0.8376094357706202</v>
+        <v>0.7795743904904525</v>
       </c>
       <c r="F34">
-        <v>68.76097391976955</v>
+        <v>72.73225537922181</v>
       </c>
       <c r="G34">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1239,19 +1239,19 @@
         <v>11</v>
       </c>
       <c r="C35">
-        <v>0.9020825838778599</v>
+        <v>0.6311146788310344</v>
       </c>
       <c r="D35">
-        <v>0.8174932397033614</v>
+        <v>0.5997317887979059</v>
       </c>
       <c r="E35">
-        <v>0.9062288246261589</v>
+        <v>0.9502738708418941</v>
       </c>
       <c r="F35">
-        <v>18.40875409656866</v>
+        <v>9.362896647441465</v>
       </c>
       <c r="G35">
-        <v>0.9419</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1265,16 +1265,16 @@
         <v>0.00270853903795504</v>
       </c>
       <c r="D36">
-        <v>0.002896533699404777</v>
+        <v>0.002610981548459045</v>
       </c>
       <c r="E36">
-        <v>1.069408141738165</v>
+        <v>0.9639815088027485</v>
       </c>
       <c r="F36">
-        <v>-4.120157460157436</v>
+        <v>-17.58495549342713</v>
       </c>
       <c r="G36">
-        <v>0.9649</v>
+        <v>0.9098000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1288,16 +1288,16 @@
         <v>0.4003187418421109</v>
       </c>
       <c r="D37">
-        <v>0.4792445461757732</v>
+        <v>0.4774459823086634</v>
       </c>
       <c r="E37">
-        <v>1.197157405047979</v>
+        <v>1.192664575512111</v>
       </c>
       <c r="F37">
-        <v>-14.10319904796176</v>
+        <v>-12.34676684772806</v>
       </c>
       <c r="G37">
-        <v>0.9321</v>
+        <v>0.9381</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1311,16 +1311,16 @@
         <v>24156.6940985472</v>
       </c>
       <c r="D38">
-        <v>31619.92494305505</v>
+        <v>33771.473115653</v>
       </c>
       <c r="E38">
-        <v>1.308950836321461</v>
+        <v>1.398017169811495</v>
       </c>
       <c r="F38">
-        <v>22.60301974965397</v>
+        <v>8.464213236996498</v>
       </c>
       <c r="G38">
-        <v>0.9883999999999999</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1334,16 +1334,16 @@
         <v>2401.857661100279</v>
       </c>
       <c r="D39">
-        <v>3639.335035052304</v>
+        <v>3856.77349636981</v>
       </c>
       <c r="E39">
-        <v>1.515216781574452</v>
+        <v>1.605746068483943</v>
       </c>
       <c r="F39">
-        <v>25.53518219078407</v>
+        <v>10.81844726645129</v>
       </c>
       <c r="G39">
-        <v>0.9857</v>
+        <v>0.9744</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1354,19 +1354,19 @@
         <v>11</v>
       </c>
       <c r="C40">
-        <v>0.8999671025432854</v>
+        <v>0.6299823871479038</v>
       </c>
       <c r="D40">
-        <v>0.8932063153807182</v>
+        <v>0.6267174989021257</v>
       </c>
       <c r="E40">
-        <v>0.9924877396701931</v>
+        <v>0.9948174928182372</v>
       </c>
       <c r="F40">
-        <v>19.79600477511704</v>
+        <v>1.236261885630641</v>
       </c>
       <c r="G40">
-        <v>0.981</v>
+        <v>0.9518</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1380,16 +1380,16 @@
         <v>0.002736347594884117</v>
       </c>
       <c r="D41">
-        <v>0.002570926845802939</v>
+        <v>0.002833780696133257</v>
       </c>
       <c r="E41">
-        <v>0.9395468801586285</v>
+        <v>1.035606989927486</v>
       </c>
       <c r="F41">
-        <v>-7.509272675734402</v>
+        <v>-8.734281869129656</v>
       </c>
       <c r="G41">
-        <v>0.916</v>
+        <v>0.9549</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1403,16 +1403,16 @@
         <v>0.3996766424448195</v>
       </c>
       <c r="D42">
-        <v>0.7521931877717514</v>
+        <v>0.8569258522026952</v>
       </c>
       <c r="E42">
-        <v>1.882004370259394</v>
+        <v>2.144047865696842</v>
       </c>
       <c r="F42">
-        <v>-51.33442521511869</v>
+        <v>-62.94603230982303</v>
       </c>
       <c r="G42">
-        <v>0.5565</v>
+        <v>0.3712</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1426,16 +1426,16 @@
         <v>6501.897312973037</v>
       </c>
       <c r="D43">
-        <v>11709.29629203002</v>
+        <v>11983.08803944169</v>
       </c>
       <c r="E43">
-        <v>1.800904525001774</v>
+        <v>1.8430140407681</v>
       </c>
       <c r="F43">
-        <v>-11.20382814051577</v>
+        <v>-30.80702268568029</v>
       </c>
       <c r="G43">
-        <v>0.6585</v>
+        <v>0.6173</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1449,16 +1449,16 @@
         <v>648.86050619293</v>
       </c>
       <c r="D44">
-        <v>2132.736716058769</v>
+        <v>2519.881441031651</v>
       </c>
       <c r="E44">
-        <v>3.28689555875763</v>
+        <v>3.883548801292582</v>
       </c>
       <c r="F44">
-        <v>-23.07078154181141</v>
+        <v>-14.71772872006072</v>
       </c>
       <c r="G44">
-        <v>0.0741</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1469,19 +1469,19 @@
         <v>11</v>
       </c>
       <c r="C45">
-        <v>0.8986863986852833</v>
+        <v>0.6292965981454346</v>
       </c>
       <c r="D45">
-        <v>0.7671325084228613</v>
+        <v>0.5953177641859446</v>
       </c>
       <c r="E45">
-        <v>0.853615354082496</v>
+        <v>0.9460050569800836</v>
       </c>
       <c r="F45">
-        <v>18.65124875770984</v>
+        <v>2.295515627570321</v>
       </c>
       <c r="G45">
-        <v>0.9026</v>
+        <v>0.9329</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1495,16 +1495,16 @@
         <v>0.002726189364700541</v>
       </c>
       <c r="D46">
-        <v>0.003494421840469704</v>
+        <v>0.002635408997169861</v>
       </c>
       <c r="E46">
-        <v>1.281797180238633</v>
+        <v>0.966700637635034</v>
       </c>
       <c r="F46">
-        <v>-175.4221875551951</v>
+        <v>15.78507864127734</v>
       </c>
       <c r="G46">
-        <v>0.832</v>
+        <v>0.9817</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1518,16 +1518,16 @@
         <v>0.4012930565270544</v>
       </c>
       <c r="D47">
-        <v>0.4000001147784777</v>
+        <v>0.3734512422014294</v>
       </c>
       <c r="E47">
-        <v>0.9967780610016871</v>
+        <v>0.9306197456627364</v>
       </c>
       <c r="F47">
-        <v>0.2625274200978356</v>
+        <v>10.29074987274472</v>
       </c>
       <c r="G47">
-        <v>0.9518</v>
+        <v>0.9653</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1541,16 +1541,16 @@
         <v>75177.41736223314</v>
       </c>
       <c r="D48">
-        <v>59263.57958680303</v>
+        <v>56960.34212432522</v>
       </c>
       <c r="E48">
-        <v>0.7883162479664438</v>
+        <v>0.7576788897903849</v>
       </c>
       <c r="F48">
-        <v>16.5927775643204</v>
+        <v>23.36379195240511</v>
       </c>
       <c r="G48">
-        <v>0.9165</v>
+        <v>0.9147999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1564,16 +1564,16 @@
         <v>7539.611827791938</v>
       </c>
       <c r="D49">
-        <v>5850.533385420926</v>
+        <v>5196.993139303906</v>
       </c>
       <c r="E49">
-        <v>0.7759727581538268</v>
+        <v>0.6892918704577269</v>
       </c>
       <c r="F49">
-        <v>21.66963380351991</v>
+        <v>34.82224941685816</v>
       </c>
       <c r="G49">
-        <v>0.9487</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1584,19 +1584,19 @@
         <v>11</v>
       </c>
       <c r="C50">
-        <v>0.9014133859409899</v>
+        <v>0.6307565644494701</v>
       </c>
       <c r="D50">
-        <v>0.7869662239454778</v>
+        <v>0.5948339731889007</v>
       </c>
       <c r="E50">
-        <v>0.8730358747934055</v>
+        <v>0.9430484068098079</v>
       </c>
       <c r="F50">
-        <v>23.88396292260997</v>
+        <v>12.43302388937852</v>
       </c>
       <c r="G50">
-        <v>0.9350000000000001</v>
+        <v>0.9529</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1610,16 +1610,16 @@
         <v>0.00272196096457235</v>
       </c>
       <c r="D51">
-        <v>0.002900116271174389</v>
+        <v>0.002171164973945787</v>
       </c>
       <c r="E51">
-        <v>1.065451087991642</v>
+        <v>0.7976473587257712</v>
       </c>
       <c r="F51">
-        <v>-46.05382178099888</v>
+        <v>11.69536661727856</v>
       </c>
       <c r="G51">
-        <v>0.9042</v>
+        <v>0.8964</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1633,16 +1633,16 @@
         <v>0.4029402263300133</v>
       </c>
       <c r="D52">
-        <v>0.4636969650085683</v>
+        <v>0.4428392928255682</v>
       </c>
       <c r="E52">
-        <v>1.15078350263494</v>
+        <v>1.099019814573879</v>
       </c>
       <c r="F52">
-        <v>-11.31630491017335</v>
+        <v>-5.724921373340952</v>
       </c>
       <c r="G52">
-        <v>0.9354</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1656,16 +1656,16 @@
         <v>24545.47486567834</v>
       </c>
       <c r="D53">
-        <v>31956.9160721061</v>
+        <v>29130.88578032798</v>
       </c>
       <c r="E53">
-        <v>1.301947354735886</v>
+        <v>1.18681288260841</v>
       </c>
       <c r="F53">
-        <v>32.24616147912032</v>
+        <v>55.00466702866365</v>
       </c>
       <c r="G53">
-        <v>0.9932</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1679,16 +1679,16 @@
         <v>2465.079302882296</v>
       </c>
       <c r="D54">
-        <v>3540.94085454916</v>
+        <v>3056.430257368051</v>
       </c>
       <c r="E54">
-        <v>1.43644094955035</v>
+        <v>1.239891249662563</v>
       </c>
       <c r="F54">
-        <v>37.40052363414716</v>
+        <v>55.75301693100008</v>
       </c>
       <c r="G54">
-        <v>0.9927</v>
+        <v>0.9988</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1699,19 +1699,19 @@
         <v>11</v>
       </c>
       <c r="C55">
-        <v>0.9019236808160245</v>
+        <v>0.6310296491565335</v>
       </c>
       <c r="D55">
-        <v>0.8018514218993591</v>
+        <v>0.5847776269651983</v>
       </c>
       <c r="E55">
-        <v>0.8890457573681578</v>
+        <v>0.9267038842736502</v>
       </c>
       <c r="F55">
-        <v>22.14768964777288</v>
+        <v>9.304532622658467</v>
       </c>
       <c r="G55">
-        <v>0.9361</v>
+        <v>0.9364</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1725,16 +1725,16 @@
         <v>0.002727433838132664</v>
       </c>
       <c r="D56">
-        <v>0.003171643213080043</v>
+        <v>0.003085063990394386</v>
       </c>
       <c r="E56">
-        <v>1.162867149602979</v>
+        <v>1.131123309853255</v>
       </c>
       <c r="F56">
-        <v>-30.83391831634061</v>
+        <v>-10.41989807304864</v>
       </c>
       <c r="G56">
-        <v>0.9392</v>
+        <v>0.9535</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1748,16 +1748,16 @@
         <v>0.3996540840539036</v>
       </c>
       <c r="D57">
-        <v>0.5110581539251229</v>
+        <v>0.4801429047311307</v>
       </c>
       <c r="E57">
-        <v>1.278751235921797</v>
+        <v>1.201396217100514</v>
       </c>
       <c r="F57">
-        <v>-20.69709364704113</v>
+        <v>-5.676608097541536</v>
       </c>
       <c r="G57">
-        <v>0.8959</v>
+        <v>0.9388</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1771,16 +1771,16 @@
         <v>24290.37561645494</v>
       </c>
       <c r="D58">
-        <v>27265.94232756249</v>
+        <v>19602.72185470277</v>
       </c>
       <c r="E58">
-        <v>1.122499822896597</v>
+        <v>0.8070160035492974</v>
       </c>
       <c r="F58">
-        <v>53.90843479301674</v>
+        <v>61.22000873457156</v>
       </c>
       <c r="G58">
-        <v>0.9975000000000001</v>
+        <v>0.9997</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1794,16 +1794,16 @@
         <v>2399.387935514007</v>
       </c>
       <c r="D59">
-        <v>3340.838090323099</v>
+        <v>2147.255756195835</v>
       </c>
       <c r="E59">
-        <v>1.39237096297536</v>
+        <v>0.8949181265829116</v>
       </c>
       <c r="F59">
-        <v>52.66873739752134</v>
+        <v>65.40817891462669</v>
       </c>
       <c r="G59">
-        <v>0.9985000000000001</v>
+        <v>0.9986</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1814,19 +1814,19 @@
         <v>11</v>
       </c>
       <c r="C60">
-        <v>0.8976700037457808</v>
+        <v>0.628752177334631</v>
       </c>
       <c r="D60">
-        <v>0.7924530485785564</v>
+        <v>0.5645621699252124</v>
       </c>
       <c r="E60">
-        <v>0.8827888258177536</v>
+        <v>0.8979088904605801</v>
       </c>
       <c r="F60">
-        <v>20.46895795071957</v>
+        <v>12.40953360181632</v>
       </c>
       <c r="G60">
-        <v>0.9275</v>
+        <v>0.9124</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1840,16 +1840,16 @@
         <v>0.002726691016454644</v>
       </c>
       <c r="D61">
-        <v>0.003520761744605914</v>
+        <v>0.002822389525202496</v>
       </c>
       <c r="E61">
-        <v>1.291221382752694</v>
+        <v>1.035096939172919</v>
       </c>
       <c r="F61">
-        <v>-84.69145093409296</v>
+        <v>-24.13526294532193</v>
       </c>
       <c r="G61">
-        <v>0.8686</v>
+        <v>0.958</v>
       </c>
     </row>
     <row r="62" spans="1:7">
